--- a/test_data/gwangju_4dong_test_orders_65.xlsx
+++ b/test_data/gwangju_4dong_test_orders_65.xlsx
@@ -6,7 +6,7 @@
     <sheet name="테스트명단" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'테스트명단'!A1:H66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'테스트명단'!A1:J66</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,1738 +400,2136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:J66"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="42.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="24.83203125" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="34.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" customWidth="1"/>
+    <col min="10" max="10" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>#</v>
+      </c>
+      <c r="B1" t="str">
         <v>성명</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>전화번호</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>배송동</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>주소</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>상세주소</v>
+      </c>
+      <c r="G1" t="str">
         <v>물품내역</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>코드</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>수량</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>요청사항</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
         <v>테스트고객001</v>
       </c>
-      <c r="B2" t="str">
+      <c r="C2" t="str">
         <v>010-5500-1001</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>경안동</v>
       </c>
-      <c r="D2" t="str">
-        <v>경기도 광주시 경안로 10, 101동 101호</v>
-      </c>
       <c r="E2" t="str">
+        <v>경기도 광주시 경안로 10</v>
+      </c>
+      <c r="F2" t="str">
+        <v>101동 101호</v>
+      </c>
+      <c r="G2" t="str">
         <v>채소</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>T0001</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>1</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
         <v>테스트고객002</v>
       </c>
-      <c r="B3" t="str">
+      <c r="C3" t="str">
         <v>010-5500-1002</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>송정동</v>
       </c>
-      <c r="D3" t="str">
-        <v>경기도 광주시 경안천로 110, 111동 102호</v>
-      </c>
       <c r="E3" t="str">
+        <v>경기도 광주시 경안천로 110</v>
+      </c>
+      <c r="F3" t="str">
+        <v>111동 102호</v>
+      </c>
+      <c r="G3" t="str">
         <v>과일</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>T0002</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
         <v>테스트고객003</v>
       </c>
-      <c r="B4" t="str">
+      <c r="C4" t="str">
         <v>010-5500-1003</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D4" t="str">
-        <v>경기도 광주시 경충대로 1407-3, 121동 103호</v>
-      </c>
       <c r="E4" t="str">
+        <v>경기도 광주시 경충대로 1407-3</v>
+      </c>
+      <c r="F4" t="str">
+        <v>121동 103호</v>
+      </c>
+      <c r="G4" t="str">
         <v>정육</v>
       </c>
-      <c r="F4" t="str">
+      <c r="H4" t="str">
         <v>T0003</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>3</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
         <v>테스트고객004</v>
       </c>
-      <c r="B5" t="str">
+      <c r="C5" t="str">
         <v>010-5500-1004</v>
       </c>
-      <c r="C5" t="str">
+      <c r="D5" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D5" t="str">
-        <v>경기도 광주시 경안로 197, 131동 104호</v>
-      </c>
       <c r="E5" t="str">
+        <v>경기도 광주시 경안로 197</v>
+      </c>
+      <c r="F5" t="str">
+        <v>131동 104호</v>
+      </c>
+      <c r="G5" t="str">
         <v>생선</v>
       </c>
-      <c r="F5" t="str">
+      <c r="H5" t="str">
         <v>T0004</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>4</v>
       </c>
-      <c r="H5" t="str">
+      <c r="J5" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
         <v>테스트고객005</v>
       </c>
-      <c r="B6" t="str">
+      <c r="C6" t="str">
         <v>010-5500-1005</v>
       </c>
-      <c r="C6" t="str">
+      <c r="D6" t="str">
         <v>경안동</v>
       </c>
-      <c r="D6" t="str">
-        <v>경기도 광주시 경안로 104, 141동 105호</v>
-      </c>
       <c r="E6" t="str">
+        <v>경기도 광주시 경안로 104</v>
+      </c>
+      <c r="F6" t="str">
+        <v>141동 105호</v>
+      </c>
+      <c r="G6" t="str">
         <v>반찬</v>
       </c>
-      <c r="F6" t="str">
+      <c r="H6" t="str">
         <v>T0005</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="H6" t="str">
+      <c r="J6" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
         <v>테스트고객006</v>
       </c>
-      <c r="B7" t="str">
+      <c r="C7" t="str">
         <v>010-5500-1006</v>
       </c>
-      <c r="C7" t="str">
+      <c r="D7" t="str">
         <v>송정동</v>
       </c>
-      <c r="D7" t="str">
-        <v>경기도 광주시 경안천로 113, 151동 106호</v>
-      </c>
       <c r="E7" t="str">
+        <v>경기도 광주시 경안천로 113</v>
+      </c>
+      <c r="F7" t="str">
+        <v>151동 106호</v>
+      </c>
+      <c r="G7" t="str">
         <v>쌀</v>
       </c>
-      <c r="F7" t="str">
+      <c r="H7" t="str">
         <v>T0006</v>
       </c>
-      <c r="G7">
+      <c r="I7">
         <v>2</v>
       </c>
-      <c r="H7" t="str">
+      <c r="J7" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
         <v>테스트고객007</v>
       </c>
-      <c r="B8" t="str">
+      <c r="C8" t="str">
         <v>010-5500-1007</v>
       </c>
-      <c r="C8" t="str">
+      <c r="D8" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D8" t="str">
-        <v>경기도 광주시 경충대로 1407-5, 161동 107호</v>
-      </c>
       <c r="E8" t="str">
+        <v>경기도 광주시 경충대로 1407-5</v>
+      </c>
+      <c r="F8" t="str">
+        <v>161동 107호</v>
+      </c>
+      <c r="G8" t="str">
         <v>두부</v>
       </c>
-      <c r="F8" t="str">
+      <c r="H8" t="str">
         <v>T0007</v>
       </c>
-      <c r="G8">
+      <c r="I8">
         <v>3</v>
       </c>
-      <c r="H8" t="str">
+      <c r="J8" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
         <v>테스트고객008</v>
       </c>
-      <c r="B9" t="str">
+      <c r="C9" t="str">
         <v>010-5500-1008</v>
       </c>
-      <c r="C9" t="str">
+      <c r="D9" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D9" t="str">
-        <v>경기도 광주시 경충대로1926번길 119, 171동 108호</v>
-      </c>
       <c r="E9" t="str">
+        <v>경기도 광주시 경충대로1926번길 119</v>
+      </c>
+      <c r="F9" t="str">
+        <v>171동 108호</v>
+      </c>
+      <c r="G9" t="str">
         <v>계란</v>
       </c>
-      <c r="F9" t="str">
+      <c r="H9" t="str">
         <v>T0008</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>4</v>
       </c>
-      <c r="H9" t="str">
+      <c r="J9" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
         <v>테스트고객009</v>
       </c>
-      <c r="B10" t="str">
+      <c r="C10" t="str">
         <v>010-5500-1009</v>
       </c>
-      <c r="C10" t="str">
+      <c r="D10" t="str">
         <v>경안동</v>
       </c>
-      <c r="D10" t="str">
-        <v>경기도 광주시 경안로 106, 181동 109호</v>
-      </c>
       <c r="E10" t="str">
+        <v>경기도 광주시 경안로 106</v>
+      </c>
+      <c r="F10" t="str">
+        <v>181동 109호</v>
+      </c>
+      <c r="G10" t="str">
         <v>건어물</v>
       </c>
-      <c r="F10" t="str">
+      <c r="H10" t="str">
         <v>T0009</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>1</v>
       </c>
-      <c r="H10" t="str">
+      <c r="J10" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
         <v>테스트고객010</v>
       </c>
-      <c r="B11" t="str">
+      <c r="C11" t="str">
         <v>010-5500-1010</v>
       </c>
-      <c r="C11" t="str">
+      <c r="D11" t="str">
         <v>송정동</v>
       </c>
-      <c r="D11" t="str">
-        <v>경기도 광주시 경안천로 114, 101동 110호</v>
-      </c>
       <c r="E11" t="str">
+        <v>경기도 광주시 경안천로 114</v>
+      </c>
+      <c r="F11" t="str">
+        <v>101동 110호</v>
+      </c>
+      <c r="G11" t="str">
         <v>생활용품</v>
       </c>
-      <c r="F11" t="str">
+      <c r="H11" t="str">
         <v>T0010</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>2</v>
       </c>
-      <c r="H11" t="str">
+      <c r="J11" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
         <v>테스트고객011</v>
       </c>
-      <c r="B12" t="str">
+      <c r="C12" t="str">
         <v>010-5500-1011</v>
       </c>
-      <c r="C12" t="str">
+      <c r="D12" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D12" t="str">
-        <v>경기도 광주시 경충대로 1407-9, 111동 111호</v>
-      </c>
       <c r="E12" t="str">
+        <v>경기도 광주시 경충대로 1407-9</v>
+      </c>
+      <c r="F12" t="str">
+        <v>111동 111호</v>
+      </c>
+      <c r="G12" t="str">
         <v>채소</v>
       </c>
-      <c r="F12" t="str">
+      <c r="H12" t="str">
         <v>T0011</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>3</v>
       </c>
-      <c r="H12" t="str">
+      <c r="J12" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
         <v>테스트고객012</v>
       </c>
-      <c r="B13" t="str">
+      <c r="C13" t="str">
         <v>010-5500-1012</v>
       </c>
-      <c r="C13" t="str">
+      <c r="D13" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D13" t="str">
-        <v>경기도 광주시 벌원길 23, 121동 112호</v>
-      </c>
       <c r="E13" t="str">
+        <v>경기도 광주시 벌원길 23</v>
+      </c>
+      <c r="F13" t="str">
+        <v>121동 112호</v>
+      </c>
+      <c r="G13" t="str">
         <v>과일</v>
       </c>
-      <c r="F13" t="str">
+      <c r="H13" t="str">
         <v>T0012</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>4</v>
       </c>
-      <c r="H13" t="str">
+      <c r="J13" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
         <v>테스트고객013</v>
       </c>
-      <c r="B14" t="str">
+      <c r="C14" t="str">
         <v>010-5500-1013</v>
       </c>
-      <c r="C14" t="str">
+      <c r="D14" t="str">
         <v>경안동</v>
       </c>
-      <c r="D14" t="str">
-        <v>경기도 광주시 경안로 112, 131동 113호</v>
-      </c>
       <c r="E14" t="str">
+        <v>경기도 광주시 경안로 112</v>
+      </c>
+      <c r="F14" t="str">
+        <v>131동 113호</v>
+      </c>
+      <c r="G14" t="str">
         <v>정육</v>
       </c>
-      <c r="F14" t="str">
+      <c r="H14" t="str">
         <v>T0013</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>1</v>
       </c>
-      <c r="H14" t="str">
+      <c r="J14" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
         <v>테스트고객014</v>
       </c>
-      <c r="B15" t="str">
+      <c r="C15" t="str">
         <v>010-5500-1014</v>
       </c>
-      <c r="C15" t="str">
+      <c r="D15" t="str">
         <v>송정동</v>
       </c>
-      <c r="D15" t="str">
-        <v>경기도 광주시 경안천로 115, 141동 114호</v>
-      </c>
       <c r="E15" t="str">
+        <v>경기도 광주시 경안천로 115</v>
+      </c>
+      <c r="F15" t="str">
+        <v>141동 114호</v>
+      </c>
+      <c r="G15" t="str">
         <v>생선</v>
       </c>
-      <c r="F15" t="str">
+      <c r="H15" t="str">
         <v>T0014</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>2</v>
       </c>
-      <c r="H15" t="str">
+      <c r="J15" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
         <v>테스트고객015</v>
       </c>
-      <c r="B16" t="str">
+      <c r="C16" t="str">
         <v>010-5500-1015</v>
       </c>
-      <c r="C16" t="str">
+      <c r="D16" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D16" t="str">
-        <v>경기도 광주시 경충대로 1411, 151동 115호</v>
-      </c>
       <c r="E16" t="str">
+        <v>경기도 광주시 경충대로 1411</v>
+      </c>
+      <c r="F16" t="str">
+        <v>151동 115호</v>
+      </c>
+      <c r="G16" t="str">
         <v>반찬</v>
       </c>
-      <c r="F16" t="str">
+      <c r="H16" t="str">
         <v>T0015</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>3</v>
       </c>
-      <c r="H16" t="str">
+      <c r="J16" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
         <v>테스트고객016</v>
       </c>
-      <c r="B17" t="str">
+      <c r="C17" t="str">
         <v>010-5500-1016</v>
       </c>
-      <c r="C17" t="str">
+      <c r="D17" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D17" t="str">
-        <v>경기도 광주시 벌원길 25, 161동 116호</v>
-      </c>
       <c r="E17" t="str">
+        <v>경기도 광주시 벌원길 25</v>
+      </c>
+      <c r="F17" t="str">
+        <v>161동 116호</v>
+      </c>
+      <c r="G17" t="str">
         <v>쌀</v>
       </c>
-      <c r="F17" t="str">
+      <c r="H17" t="str">
         <v>T0016</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>4</v>
       </c>
-      <c r="H17" t="str">
+      <c r="J17" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
         <v>테스트고객017</v>
       </c>
-      <c r="B18" t="str">
+      <c r="C18" t="str">
         <v>010-5500-1017</v>
       </c>
-      <c r="C18" t="str">
+      <c r="D18" t="str">
         <v>경안동</v>
       </c>
-      <c r="D18" t="str">
-        <v>경기도 광주시 경안로 114, 171동 117호</v>
-      </c>
       <c r="E18" t="str">
+        <v>경기도 광주시 경안로 114</v>
+      </c>
+      <c r="F18" t="str">
+        <v>171동 117호</v>
+      </c>
+      <c r="G18" t="str">
         <v>두부</v>
       </c>
-      <c r="F18" t="str">
+      <c r="H18" t="str">
         <v>T0017</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>1</v>
       </c>
-      <c r="H18" t="str">
+      <c r="J18" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
         <v>테스트고객018</v>
       </c>
-      <c r="B19" t="str">
+      <c r="C19" t="str">
         <v>010-5500-1018</v>
       </c>
-      <c r="C19" t="str">
+      <c r="D19" t="str">
         <v>송정동</v>
       </c>
-      <c r="D19" t="str">
-        <v>경기도 광주시 경안천로 117, 181동 118호</v>
-      </c>
       <c r="E19" t="str">
+        <v>경기도 광주시 경안천로 117</v>
+      </c>
+      <c r="F19" t="str">
+        <v>181동 118호</v>
+      </c>
+      <c r="G19" t="str">
         <v>계란</v>
       </c>
-      <c r="F19" t="str">
+      <c r="H19" t="str">
         <v>T0018</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>2</v>
       </c>
-      <c r="H19" t="str">
+      <c r="J19" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
         <v>테스트고객019</v>
       </c>
-      <c r="B20" t="str">
+      <c r="C20" t="str">
         <v>010-5500-1019</v>
       </c>
-      <c r="C20" t="str">
+      <c r="D20" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D20" t="str">
-        <v>경기도 광주시 경충대로 1413, 101동 119호</v>
-      </c>
       <c r="E20" t="str">
+        <v>경기도 광주시 경충대로 1413</v>
+      </c>
+      <c r="F20" t="str">
+        <v>101동 119호</v>
+      </c>
+      <c r="G20" t="str">
         <v>건어물</v>
       </c>
-      <c r="F20" t="str">
+      <c r="H20" t="str">
         <v>T0019</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>3</v>
       </c>
-      <c r="H20" t="str">
+      <c r="J20" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
         <v>테스트고객020</v>
       </c>
-      <c r="B21" t="str">
+      <c r="C21" t="str">
         <v>010-5500-1020</v>
       </c>
-      <c r="C21" t="str">
+      <c r="D21" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D21" t="str">
-        <v>경기도 광주시 벌원길 26, 111동 120호</v>
-      </c>
       <c r="E21" t="str">
+        <v>경기도 광주시 벌원길 26</v>
+      </c>
+      <c r="F21" t="str">
+        <v>111동 120호</v>
+      </c>
+      <c r="G21" t="str">
         <v>생활용품</v>
       </c>
-      <c r="F21" t="str">
+      <c r="H21" t="str">
         <v>T0020</v>
       </c>
-      <c r="G21">
+      <c r="I21">
         <v>4</v>
       </c>
-      <c r="H21" t="str">
+      <c r="J21" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
         <v>테스트고객021</v>
       </c>
-      <c r="B22" t="str">
+      <c r="C22" t="str">
         <v>010-5500-1021</v>
       </c>
-      <c r="C22" t="str">
+      <c r="D22" t="str">
         <v>경안동</v>
       </c>
-      <c r="D22" t="str">
-        <v>경기도 광주시 경안로 115, 121동 101호</v>
-      </c>
       <c r="E22" t="str">
+        <v>경기도 광주시 경안로 115</v>
+      </c>
+      <c r="F22" t="str">
+        <v>121동 101호</v>
+      </c>
+      <c r="G22" t="str">
         <v>채소</v>
       </c>
-      <c r="F22" t="str">
+      <c r="H22" t="str">
         <v>T0021</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>1</v>
       </c>
-      <c r="H22" t="str">
+      <c r="J22" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
         <v>테스트고객022</v>
       </c>
-      <c r="B23" t="str">
+      <c r="C23" t="str">
         <v>010-5500-1022</v>
       </c>
-      <c r="C23" t="str">
+      <c r="D23" t="str">
         <v>송정동</v>
       </c>
-      <c r="D23" t="str">
-        <v>경기도 광주시 경안천로 118, 131동 102호</v>
-      </c>
       <c r="E23" t="str">
+        <v>경기도 광주시 경안천로 118</v>
+      </c>
+      <c r="F23" t="str">
+        <v>131동 102호</v>
+      </c>
+      <c r="G23" t="str">
         <v>과일</v>
       </c>
-      <c r="F23" t="str">
+      <c r="H23" t="str">
         <v>T0022</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>2</v>
       </c>
-      <c r="H23" t="str">
+      <c r="J23" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
         <v>테스트고객023</v>
       </c>
-      <c r="B24" t="str">
+      <c r="C24" t="str">
         <v>010-5500-1023</v>
       </c>
-      <c r="C24" t="str">
+      <c r="D24" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D24" t="str">
-        <v>경기도 광주시 경충대로 1414, 141동 103호</v>
-      </c>
       <c r="E24" t="str">
+        <v>경기도 광주시 경충대로 1414</v>
+      </c>
+      <c r="F24" t="str">
+        <v>141동 103호</v>
+      </c>
+      <c r="G24" t="str">
         <v>정육</v>
       </c>
-      <c r="F24" t="str">
+      <c r="H24" t="str">
         <v>T0023</v>
       </c>
-      <c r="G24">
+      <c r="I24">
         <v>3</v>
       </c>
-      <c r="H24" t="str">
+      <c r="J24" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
         <v>테스트고객024</v>
       </c>
-      <c r="B25" t="str">
+      <c r="C25" t="str">
         <v>010-5500-1024</v>
       </c>
-      <c r="C25" t="str">
+      <c r="D25" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D25" t="str">
-        <v>경기도 광주시 벌원길 34, 151동 104호</v>
-      </c>
       <c r="E25" t="str">
+        <v>경기도 광주시 벌원길 34</v>
+      </c>
+      <c r="F25" t="str">
+        <v>151동 104호</v>
+      </c>
+      <c r="G25" t="str">
         <v>생선</v>
       </c>
-      <c r="F25" t="str">
+      <c r="H25" t="str">
         <v>T0024</v>
       </c>
-      <c r="G25">
+      <c r="I25">
         <v>4</v>
       </c>
-      <c r="H25" t="str">
+      <c r="J25" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
         <v>테스트고객025</v>
       </c>
-      <c r="B26" t="str">
+      <c r="C26" t="str">
         <v>010-5500-1025</v>
       </c>
-      <c r="C26" t="str">
+      <c r="D26" t="str">
         <v>경안동</v>
       </c>
-      <c r="D26" t="str">
-        <v>경기도 광주시 경안로 116, 161동 105호</v>
-      </c>
       <c r="E26" t="str">
+        <v>경기도 광주시 경안로 116</v>
+      </c>
+      <c r="F26" t="str">
+        <v>161동 105호</v>
+      </c>
+      <c r="G26" t="str">
         <v>반찬</v>
       </c>
-      <c r="F26" t="str">
+      <c r="H26" t="str">
         <v>T0025</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>1</v>
       </c>
-      <c r="H26" t="str">
+      <c r="J26" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
         <v>테스트고객026</v>
       </c>
-      <c r="B27" t="str">
+      <c r="C27" t="str">
         <v>010-5500-1026</v>
       </c>
-      <c r="C27" t="str">
+      <c r="D27" t="str">
         <v>송정동</v>
       </c>
-      <c r="D27" t="str">
-        <v>경기도 광주시 경안천로 119, 171동 106호</v>
-      </c>
       <c r="E27" t="str">
+        <v>경기도 광주시 경안천로 119</v>
+      </c>
+      <c r="F27" t="str">
+        <v>171동 106호</v>
+      </c>
+      <c r="G27" t="str">
         <v>쌀</v>
       </c>
-      <c r="F27" t="str">
+      <c r="H27" t="str">
         <v>T0026</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>2</v>
       </c>
-      <c r="H27" t="str">
+      <c r="J27" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
         <v>테스트고객027</v>
       </c>
-      <c r="B28" t="str">
+      <c r="C28" t="str">
         <v>010-5500-1027</v>
       </c>
-      <c r="C28" t="str">
+      <c r="D28" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D28" t="str">
-        <v>경기도 광주시 경충대로 1425, 181동 107호</v>
-      </c>
       <c r="E28" t="str">
+        <v>경기도 광주시 경충대로 1425</v>
+      </c>
+      <c r="F28" t="str">
+        <v>181동 107호</v>
+      </c>
+      <c r="G28" t="str">
         <v>두부</v>
       </c>
-      <c r="F28" t="str">
+      <c r="H28" t="str">
         <v>T0027</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>3</v>
       </c>
-      <c r="H28" t="str">
+      <c r="J28" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
         <v>테스트고객028</v>
       </c>
-      <c r="B29" t="str">
+      <c r="C29" t="str">
         <v>010-5500-1028</v>
       </c>
-      <c r="C29" t="str">
+      <c r="D29" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D29" t="str">
-        <v>경기도 광주시 벌원길 36, 101동 108호</v>
-      </c>
       <c r="E29" t="str">
+        <v>경기도 광주시 벌원길 36</v>
+      </c>
+      <c r="F29" t="str">
+        <v>101동 108호</v>
+      </c>
+      <c r="G29" t="str">
         <v>계란</v>
       </c>
-      <c r="F29" t="str">
+      <c r="H29" t="str">
         <v>T0028</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>4</v>
       </c>
-      <c r="H29" t="str">
+      <c r="J29" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
         <v>테스트고객029</v>
       </c>
-      <c r="B30" t="str">
+      <c r="C30" t="str">
         <v>010-5500-1029</v>
       </c>
-      <c r="C30" t="str">
+      <c r="D30" t="str">
         <v>경안동</v>
       </c>
-      <c r="D30" t="str">
-        <v>경기도 광주시 경안로 117, 111동 109호</v>
-      </c>
       <c r="E30" t="str">
+        <v>경기도 광주시 경안로 117</v>
+      </c>
+      <c r="F30" t="str">
+        <v>111동 109호</v>
+      </c>
+      <c r="G30" t="str">
         <v>건어물</v>
       </c>
-      <c r="F30" t="str">
+      <c r="H30" t="str">
         <v>T0029</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>1</v>
       </c>
-      <c r="H30" t="str">
+      <c r="J30" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
         <v>테스트고객030</v>
       </c>
-      <c r="B31" t="str">
+      <c r="C31" t="str">
         <v>010-5500-1030</v>
       </c>
-      <c r="C31" t="str">
+      <c r="D31" t="str">
         <v>송정동</v>
       </c>
-      <c r="D31" t="str">
-        <v>경기도 광주시 경안천로 121, 121동 110호</v>
-      </c>
       <c r="E31" t="str">
+        <v>경기도 광주시 경안천로 121</v>
+      </c>
+      <c r="F31" t="str">
+        <v>121동 110호</v>
+      </c>
+      <c r="G31" t="str">
         <v>생활용품</v>
       </c>
-      <c r="F31" t="str">
+      <c r="H31" t="str">
         <v>T0030</v>
       </c>
-      <c r="G31">
+      <c r="I31">
         <v>2</v>
       </c>
-      <c r="H31" t="str">
+      <c r="J31" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
         <v>테스트고객031</v>
       </c>
-      <c r="B32" t="str">
+      <c r="C32" t="str">
         <v>010-5500-1031</v>
       </c>
-      <c r="C32" t="str">
+      <c r="D32" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D32" t="str">
-        <v>경기도 광주시 경충대로 1428-14, 131동 111호</v>
-      </c>
       <c r="E32" t="str">
+        <v>경기도 광주시 경충대로 1428-14</v>
+      </c>
+      <c r="F32" t="str">
+        <v>131동 111호</v>
+      </c>
+      <c r="G32" t="str">
         <v>채소</v>
       </c>
-      <c r="F32" t="str">
+      <c r="H32" t="str">
         <v>T0031</v>
       </c>
-      <c r="G32">
+      <c r="I32">
         <v>3</v>
       </c>
-      <c r="H32" t="str">
+      <c r="J32" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
         <v>테스트고객032</v>
       </c>
-      <c r="B33" t="str">
+      <c r="C33" t="str">
         <v>010-5500-1032</v>
       </c>
-      <c r="C33" t="str">
+      <c r="D33" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D33" t="str">
-        <v>경기도 광주시 벌원길 37, 141동 112호</v>
-      </c>
       <c r="E33" t="str">
+        <v>경기도 광주시 벌원길 37</v>
+      </c>
+      <c r="F33" t="str">
+        <v>141동 112호</v>
+      </c>
+      <c r="G33" t="str">
         <v>과일</v>
       </c>
-      <c r="F33" t="str">
+      <c r="H33" t="str">
         <v>T0032</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>4</v>
       </c>
-      <c r="H33" t="str">
+      <c r="J33" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
         <v>테스트고객033</v>
       </c>
-      <c r="B34" t="str">
+      <c r="C34" t="str">
         <v>010-5500-1033</v>
       </c>
-      <c r="C34" t="str">
+      <c r="D34" t="str">
         <v>경안동</v>
       </c>
-      <c r="D34" t="str">
-        <v>경기도 광주시 경안로 117-15, 151동 113호</v>
-      </c>
       <c r="E34" t="str">
+        <v>경기도 광주시 경안로 117-15</v>
+      </c>
+      <c r="F34" t="str">
+        <v>151동 113호</v>
+      </c>
+      <c r="G34" t="str">
         <v>정육</v>
       </c>
-      <c r="F34" t="str">
+      <c r="H34" t="str">
         <v>T0033</v>
       </c>
-      <c r="G34">
+      <c r="I34">
         <v>1</v>
       </c>
-      <c r="H34" t="str">
+      <c r="J34" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
         <v>테스트고객034</v>
       </c>
-      <c r="B35" t="str">
+      <c r="C35" t="str">
         <v>010-5500-1034</v>
       </c>
-      <c r="C35" t="str">
+      <c r="D35" t="str">
         <v>송정동</v>
       </c>
-      <c r="D35" t="str">
-        <v>경기도 광주시 경안천로 122, 161동 114호</v>
-      </c>
       <c r="E35" t="str">
+        <v>경기도 광주시 경안천로 122</v>
+      </c>
+      <c r="F35" t="str">
+        <v>161동 114호</v>
+      </c>
+      <c r="G35" t="str">
         <v>생선</v>
       </c>
-      <c r="F35" t="str">
+      <c r="H35" t="str">
         <v>T0034</v>
       </c>
-      <c r="G35">
+      <c r="I35">
         <v>2</v>
       </c>
-      <c r="H35" t="str">
+      <c r="J35" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
         <v>테스트고객035</v>
       </c>
-      <c r="B36" t="str">
+      <c r="C36" t="str">
         <v>010-5500-1035</v>
       </c>
-      <c r="C36" t="str">
+      <c r="D36" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D36" t="str">
-        <v>경기도 광주시 경충대로 1428-15, 171동 115호</v>
-      </c>
       <c r="E36" t="str">
+        <v>경기도 광주시 경충대로 1428-15</v>
+      </c>
+      <c r="F36" t="str">
+        <v>171동 115호</v>
+      </c>
+      <c r="G36" t="str">
         <v>반찬</v>
       </c>
-      <c r="F36" t="str">
+      <c r="H36" t="str">
         <v>T0035</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>3</v>
       </c>
-      <c r="H36" t="str">
+      <c r="J36" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
         <v>테스트고객036</v>
       </c>
-      <c r="B37" t="str">
+      <c r="C37" t="str">
         <v>010-5500-1036</v>
       </c>
-      <c r="C37" t="str">
+      <c r="D37" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D37" t="str">
-        <v>경기도 광주시 벌원길 37-4, 181동 116호</v>
-      </c>
       <c r="E37" t="str">
+        <v>경기도 광주시 벌원길 37-4</v>
+      </c>
+      <c r="F37" t="str">
+        <v>181동 116호</v>
+      </c>
+      <c r="G37" t="str">
         <v>쌀</v>
       </c>
-      <c r="F37" t="str">
+      <c r="H37" t="str">
         <v>T0036</v>
       </c>
-      <c r="G37">
+      <c r="I37">
         <v>4</v>
       </c>
-      <c r="H37" t="str">
+      <c r="J37" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
         <v>테스트고객037</v>
       </c>
-      <c r="B38" t="str">
+      <c r="C38" t="str">
         <v>010-5500-1037</v>
       </c>
-      <c r="C38" t="str">
+      <c r="D38" t="str">
         <v>경안동</v>
       </c>
-      <c r="D38" t="str">
-        <v>경기도 광주시 경안로 118, 101동 117호</v>
-      </c>
       <c r="E38" t="str">
+        <v>경기도 광주시 경안로 118</v>
+      </c>
+      <c r="F38" t="str">
+        <v>101동 117호</v>
+      </c>
+      <c r="G38" t="str">
         <v>두부</v>
       </c>
-      <c r="F38" t="str">
+      <c r="H38" t="str">
         <v>T0037</v>
       </c>
-      <c r="G38">
+      <c r="I38">
         <v>1</v>
       </c>
-      <c r="H38" t="str">
+      <c r="J38" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="str">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
         <v>테스트고객038</v>
       </c>
-      <c r="B39" t="str">
+      <c r="C39" t="str">
         <v>010-5500-1038</v>
       </c>
-      <c r="C39" t="str">
+      <c r="D39" t="str">
         <v>송정동</v>
       </c>
-      <c r="D39" t="str">
-        <v>경기도 광주시 경안천로 124, 111동 118호</v>
-      </c>
       <c r="E39" t="str">
+        <v>경기도 광주시 경안천로 124</v>
+      </c>
+      <c r="F39" t="str">
+        <v>111동 118호</v>
+      </c>
+      <c r="G39" t="str">
         <v>계란</v>
       </c>
-      <c r="F39" t="str">
+      <c r="H39" t="str">
         <v>T0038</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>2</v>
       </c>
-      <c r="H39" t="str">
+      <c r="J39" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="str">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
         <v>테스트고객039</v>
       </c>
-      <c r="B40" t="str">
+      <c r="C40" t="str">
         <v>010-5500-1039</v>
       </c>
-      <c r="C40" t="str">
+      <c r="D40" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D40" t="str">
-        <v>경기도 광주시 경충대로 1428-17, 121동 119호</v>
-      </c>
       <c r="E40" t="str">
+        <v>경기도 광주시 경충대로 1428-17</v>
+      </c>
+      <c r="F40" t="str">
+        <v>121동 119호</v>
+      </c>
+      <c r="G40" t="str">
         <v>건어물</v>
       </c>
-      <c r="F40" t="str">
+      <c r="H40" t="str">
         <v>T0039</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>3</v>
       </c>
-      <c r="H40" t="str">
+      <c r="J40" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="str">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
         <v>테스트고객040</v>
       </c>
-      <c r="B41" t="str">
+      <c r="C41" t="str">
         <v>010-5500-1040</v>
       </c>
-      <c r="C41" t="str">
+      <c r="D41" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D41" t="str">
-        <v>경기도 광주시 벌원길 37-5, 131동 120호</v>
-      </c>
       <c r="E41" t="str">
+        <v>경기도 광주시 벌원길 37-5</v>
+      </c>
+      <c r="F41" t="str">
+        <v>131동 120호</v>
+      </c>
+      <c r="G41" t="str">
         <v>생활용품</v>
       </c>
-      <c r="F41" t="str">
+      <c r="H41" t="str">
         <v>T0040</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>4</v>
       </c>
-      <c r="H41" t="str">
+      <c r="J41" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="str">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
         <v>테스트고객041</v>
       </c>
-      <c r="B42" t="str">
+      <c r="C42" t="str">
         <v>010-5500-1041</v>
       </c>
-      <c r="C42" t="str">
+      <c r="D42" t="str">
         <v>경안동</v>
       </c>
-      <c r="D42" t="str">
-        <v>경기도 광주시 경안로 119, 141동 101호</v>
-      </c>
       <c r="E42" t="str">
+        <v>경기도 광주시 경안로 119</v>
+      </c>
+      <c r="F42" t="str">
+        <v>141동 101호</v>
+      </c>
+      <c r="G42" t="str">
         <v>채소</v>
       </c>
-      <c r="F42" t="str">
+      <c r="H42" t="str">
         <v>T0041</v>
       </c>
-      <c r="G42">
+      <c r="I42">
         <v>1</v>
       </c>
-      <c r="H42" t="str">
+      <c r="J42" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="str">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
         <v>테스트고객042</v>
       </c>
-      <c r="B43" t="str">
+      <c r="C43" t="str">
         <v>010-5500-1042</v>
       </c>
-      <c r="C43" t="str">
+      <c r="D43" t="str">
         <v>송정동</v>
       </c>
-      <c r="D43" t="str">
-        <v>경기도 광주시 경안천로 124-1, 151동 102호</v>
-      </c>
       <c r="E43" t="str">
+        <v>경기도 광주시 경안천로 124-1</v>
+      </c>
+      <c r="F43" t="str">
+        <v>151동 102호</v>
+      </c>
+      <c r="G43" t="str">
         <v>과일</v>
       </c>
-      <c r="F43" t="str">
+      <c r="H43" t="str">
         <v>T0042</v>
       </c>
-      <c r="G43">
+      <c r="I43">
         <v>2</v>
       </c>
-      <c r="H43" t="str">
+      <c r="J43" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="str">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
         <v>테스트고객043</v>
       </c>
-      <c r="B44" t="str">
+      <c r="C44" t="str">
         <v>010-5500-1043</v>
       </c>
-      <c r="C44" t="str">
+      <c r="D44" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D44" t="str">
-        <v>경기도 광주시 경충대로 1428-19, 161동 103호</v>
-      </c>
       <c r="E44" t="str">
+        <v>경기도 광주시 경충대로 1428-19</v>
+      </c>
+      <c r="F44" t="str">
+        <v>161동 103호</v>
+      </c>
+      <c r="G44" t="str">
         <v>정육</v>
       </c>
-      <c r="F44" t="str">
+      <c r="H44" t="str">
         <v>T0043</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>3</v>
       </c>
-      <c r="H44" t="str">
+      <c r="J44" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="str">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
         <v>테스트고객044</v>
       </c>
-      <c r="B45" t="str">
+      <c r="C45" t="str">
         <v>010-5500-1044</v>
       </c>
-      <c r="C45" t="str">
+      <c r="D45" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D45" t="str">
-        <v>경기도 광주시 벌원길 37-7, 171동 104호</v>
-      </c>
       <c r="E45" t="str">
+        <v>경기도 광주시 벌원길 37-7</v>
+      </c>
+      <c r="F45" t="str">
+        <v>171동 104호</v>
+      </c>
+      <c r="G45" t="str">
         <v>생선</v>
       </c>
-      <c r="F45" t="str">
+      <c r="H45" t="str">
         <v>T0044</v>
       </c>
-      <c r="G45">
+      <c r="I45">
         <v>4</v>
       </c>
-      <c r="H45" t="str">
+      <c r="J45" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="str">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
         <v>테스트고객045</v>
       </c>
-      <c r="B46" t="str">
+      <c r="C46" t="str">
         <v>010-5500-1045</v>
       </c>
-      <c r="C46" t="str">
+      <c r="D46" t="str">
         <v>경안동</v>
       </c>
-      <c r="D46" t="str">
-        <v>경기도 광주시 경안로 120, 181동 105호</v>
-      </c>
       <c r="E46" t="str">
+        <v>경기도 광주시 경안로 120</v>
+      </c>
+      <c r="F46" t="str">
+        <v>181동 105호</v>
+      </c>
+      <c r="G46" t="str">
         <v>반찬</v>
       </c>
-      <c r="F46" t="str">
+      <c r="H46" t="str">
         <v>T0045</v>
       </c>
-      <c r="G46">
+      <c r="I46">
         <v>1</v>
       </c>
-      <c r="H46" t="str">
+      <c r="J46" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="str">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
         <v>테스트고객046</v>
       </c>
-      <c r="B47" t="str">
+      <c r="C47" t="str">
         <v>010-5500-1046</v>
       </c>
-      <c r="C47" t="str">
+      <c r="D47" t="str">
         <v>송정동</v>
       </c>
-      <c r="D47" t="str">
-        <v>경기도 광주시 경안천로 126, 101동 106호</v>
-      </c>
       <c r="E47" t="str">
+        <v>경기도 광주시 경안천로 126</v>
+      </c>
+      <c r="F47" t="str">
+        <v>101동 106호</v>
+      </c>
+      <c r="G47" t="str">
         <v>쌀</v>
       </c>
-      <c r="F47" t="str">
+      <c r="H47" t="str">
         <v>T0046</v>
       </c>
-      <c r="G47">
+      <c r="I47">
         <v>2</v>
       </c>
-      <c r="H47" t="str">
+      <c r="J47" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="str">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
         <v>테스트고객047</v>
       </c>
-      <c r="B48" t="str">
+      <c r="C48" t="str">
         <v>010-5500-1047</v>
       </c>
-      <c r="C48" t="str">
+      <c r="D48" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D48" t="str">
-        <v>경기도 광주시 경충대로 1429, 111동 107호</v>
-      </c>
       <c r="E48" t="str">
+        <v>경기도 광주시 경충대로 1429</v>
+      </c>
+      <c r="F48" t="str">
+        <v>111동 107호</v>
+      </c>
+      <c r="G48" t="str">
         <v>두부</v>
       </c>
-      <c r="F48" t="str">
+      <c r="H48" t="str">
         <v>T0047</v>
       </c>
-      <c r="G48">
+      <c r="I48">
         <v>3</v>
       </c>
-      <c r="H48" t="str">
+      <c r="J48" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="str">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
         <v>테스트고객048</v>
       </c>
-      <c r="B49" t="str">
+      <c r="C49" t="str">
         <v>010-5500-1048</v>
       </c>
-      <c r="C49" t="str">
+      <c r="D49" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D49" t="str">
-        <v>경기도 광주시 벌원길 38, 121동 108호</v>
-      </c>
       <c r="E49" t="str">
+        <v>경기도 광주시 벌원길 38</v>
+      </c>
+      <c r="F49" t="str">
+        <v>121동 108호</v>
+      </c>
+      <c r="G49" t="str">
         <v>계란</v>
       </c>
-      <c r="F49" t="str">
+      <c r="H49" t="str">
         <v>T0048</v>
       </c>
-      <c r="G49">
+      <c r="I49">
         <v>4</v>
       </c>
-      <c r="H49" t="str">
+      <c r="J49" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
         <v>테스트고객049</v>
       </c>
-      <c r="B50" t="str">
+      <c r="C50" t="str">
         <v>010-5500-1049</v>
       </c>
-      <c r="C50" t="str">
+      <c r="D50" t="str">
         <v>경안동</v>
       </c>
-      <c r="D50" t="str">
-        <v>경기도 광주시 경안로 121, 131동 109호</v>
-      </c>
       <c r="E50" t="str">
+        <v>경기도 광주시 경안로 121</v>
+      </c>
+      <c r="F50" t="str">
+        <v>131동 109호</v>
+      </c>
+      <c r="G50" t="str">
         <v>건어물</v>
       </c>
-      <c r="F50" t="str">
+      <c r="H50" t="str">
         <v>T0049</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>1</v>
       </c>
-      <c r="H50" t="str">
+      <c r="J50" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="str">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
         <v>테스트고객050</v>
       </c>
-      <c r="B51" t="str">
+      <c r="C51" t="str">
         <v>010-5500-1050</v>
       </c>
-      <c r="C51" t="str">
+      <c r="D51" t="str">
         <v>송정동</v>
       </c>
-      <c r="D51" t="str">
-        <v>경기도 광주시 경안천로 127, 141동 110호</v>
-      </c>
       <c r="E51" t="str">
+        <v>경기도 광주시 경안천로 127</v>
+      </c>
+      <c r="F51" t="str">
+        <v>141동 110호</v>
+      </c>
+      <c r="G51" t="str">
         <v>생활용품</v>
       </c>
-      <c r="F51" t="str">
+      <c r="H51" t="str">
         <v>T0050</v>
       </c>
-      <c r="G51">
+      <c r="I51">
         <v>2</v>
       </c>
-      <c r="H51" t="str">
+      <c r="J51" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="str">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
         <v>테스트고객051</v>
       </c>
-      <c r="B52" t="str">
+      <c r="C52" t="str">
         <v>010-5500-1051</v>
       </c>
-      <c r="C52" t="str">
+      <c r="D52" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D52" t="str">
-        <v>경기도 광주시 경충대로 1430, 151동 111호</v>
-      </c>
       <c r="E52" t="str">
+        <v>경기도 광주시 경충대로 1430</v>
+      </c>
+      <c r="F52" t="str">
+        <v>151동 111호</v>
+      </c>
+      <c r="G52" t="str">
         <v>채소</v>
       </c>
-      <c r="F52" t="str">
+      <c r="H52" t="str">
         <v>T0051</v>
       </c>
-      <c r="G52">
+      <c r="I52">
         <v>3</v>
       </c>
-      <c r="H52" t="str">
+      <c r="J52" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="str">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
         <v>테스트고객052</v>
       </c>
-      <c r="B53" t="str">
+      <c r="C53" t="str">
         <v>010-5500-1052</v>
       </c>
-      <c r="C53" t="str">
+      <c r="D53" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D53" t="str">
-        <v>경기도 광주시 벌원길 4, 161동 112호</v>
-      </c>
       <c r="E53" t="str">
+        <v>경기도 광주시 벌원길 4</v>
+      </c>
+      <c r="F53" t="str">
+        <v>161동 112호</v>
+      </c>
+      <c r="G53" t="str">
         <v>과일</v>
       </c>
-      <c r="F53" t="str">
+      <c r="H53" t="str">
         <v>T0052</v>
       </c>
-      <c r="G53">
+      <c r="I53">
         <v>4</v>
       </c>
-      <c r="H53" t="str">
+      <c r="J53" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="str">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
         <v>테스트고객053</v>
       </c>
-      <c r="B54" t="str">
+      <c r="C54" t="str">
         <v>010-5500-1053</v>
       </c>
-      <c r="C54" t="str">
+      <c r="D54" t="str">
         <v>경안동</v>
       </c>
-      <c r="D54" t="str">
-        <v>경기도 광주시 경안로 122, 171동 113호</v>
-      </c>
       <c r="E54" t="str">
+        <v>경기도 광주시 경안로 122</v>
+      </c>
+      <c r="F54" t="str">
+        <v>171동 113호</v>
+      </c>
+      <c r="G54" t="str">
         <v>정육</v>
       </c>
-      <c r="F54" t="str">
+      <c r="H54" t="str">
         <v>T0053</v>
       </c>
-      <c r="G54">
+      <c r="I54">
         <v>1</v>
       </c>
-      <c r="H54" t="str">
+      <c r="J54" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="str">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
         <v>테스트고객054</v>
       </c>
-      <c r="B55" t="str">
+      <c r="C55" t="str">
         <v>010-5500-1054</v>
       </c>
-      <c r="C55" t="str">
+      <c r="D55" t="str">
         <v>송정동</v>
       </c>
-      <c r="D55" t="str">
-        <v>경기도 광주시 경안천로 129, 181동 114호</v>
-      </c>
       <c r="E55" t="str">
+        <v>경기도 광주시 경안천로 129</v>
+      </c>
+      <c r="F55" t="str">
+        <v>181동 114호</v>
+      </c>
+      <c r="G55" t="str">
         <v>생선</v>
       </c>
-      <c r="F55" t="str">
+      <c r="H55" t="str">
         <v>T0054</v>
       </c>
-      <c r="G55">
+      <c r="I55">
         <v>2</v>
       </c>
-      <c r="H55" t="str">
+      <c r="J55" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="str">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
         <v>테스트고객055</v>
       </c>
-      <c r="B56" t="str">
+      <c r="C56" t="str">
         <v>010-5500-1055</v>
       </c>
-      <c r="C56" t="str">
+      <c r="D56" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D56" t="str">
-        <v>경기도 광주시 경충대로 1436, 101동 115호</v>
-      </c>
       <c r="E56" t="str">
+        <v>경기도 광주시 경충대로 1436</v>
+      </c>
+      <c r="F56" t="str">
+        <v>101동 115호</v>
+      </c>
+      <c r="G56" t="str">
         <v>반찬</v>
       </c>
-      <c r="F56" t="str">
+      <c r="H56" t="str">
         <v>T0055</v>
       </c>
-      <c r="G56">
+      <c r="I56">
         <v>3</v>
       </c>
-      <c r="H56" t="str">
+      <c r="J56" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
         <v>테스트고객056</v>
       </c>
-      <c r="B57" t="str">
+      <c r="C57" t="str">
         <v>010-5500-1056</v>
       </c>
-      <c r="C57" t="str">
+      <c r="D57" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D57" t="str">
-        <v>경기도 광주시 벌원길 40, 111동 116호</v>
-      </c>
       <c r="E57" t="str">
+        <v>경기도 광주시 벌원길 40</v>
+      </c>
+      <c r="F57" t="str">
+        <v>111동 116호</v>
+      </c>
+      <c r="G57" t="str">
         <v>쌀</v>
       </c>
-      <c r="F57" t="str">
+      <c r="H57" t="str">
         <v>T0056</v>
       </c>
-      <c r="G57">
+      <c r="I57">
         <v>4</v>
       </c>
-      <c r="H57" t="str">
+      <c r="J57" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="str">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
         <v>테스트고객057</v>
       </c>
-      <c r="B58" t="str">
+      <c r="C58" t="str">
         <v>010-5500-1057</v>
       </c>
-      <c r="C58" t="str">
+      <c r="D58" t="str">
         <v>경안동</v>
       </c>
-      <c r="D58" t="str">
-        <v>경기도 광주시 경안로 123-10, 121동 117호</v>
-      </c>
       <c r="E58" t="str">
+        <v>경기도 광주시 경안로 123-10</v>
+      </c>
+      <c r="F58" t="str">
+        <v>121동 117호</v>
+      </c>
+      <c r="G58" t="str">
         <v>두부</v>
       </c>
-      <c r="F58" t="str">
+      <c r="H58" t="str">
         <v>T0057</v>
       </c>
-      <c r="G58">
+      <c r="I58">
         <v>1</v>
       </c>
-      <c r="H58" t="str">
+      <c r="J58" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="str">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
         <v>테스트고객058</v>
       </c>
-      <c r="B59" t="str">
+      <c r="C59" t="str">
         <v>010-5500-1058</v>
       </c>
-      <c r="C59" t="str">
+      <c r="D59" t="str">
         <v>송정동</v>
       </c>
-      <c r="D59" t="str">
-        <v>경기도 광주시 경안천로 13, 131동 118호</v>
-      </c>
       <c r="E59" t="str">
+        <v>경기도 광주시 경안천로 13</v>
+      </c>
+      <c r="F59" t="str">
+        <v>131동 118호</v>
+      </c>
+      <c r="G59" t="str">
         <v>계란</v>
       </c>
-      <c r="F59" t="str">
+      <c r="H59" t="str">
         <v>T0058</v>
       </c>
-      <c r="G59">
+      <c r="I59">
         <v>2</v>
       </c>
-      <c r="H59" t="str">
+      <c r="J59" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="str">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
         <v>테스트고객059</v>
       </c>
-      <c r="B60" t="str">
+      <c r="C60" t="str">
         <v>010-5500-1059</v>
       </c>
-      <c r="C60" t="str">
+      <c r="D60" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D60" t="str">
-        <v>경기도 광주시 경충대로 1438, 141동 119호</v>
-      </c>
       <c r="E60" t="str">
+        <v>경기도 광주시 경충대로 1438</v>
+      </c>
+      <c r="F60" t="str">
+        <v>141동 119호</v>
+      </c>
+      <c r="G60" t="str">
         <v>건어물</v>
       </c>
-      <c r="F60" t="str">
+      <c r="H60" t="str">
         <v>T0059</v>
       </c>
-      <c r="G60">
+      <c r="I60">
         <v>3</v>
       </c>
-      <c r="H60" t="str">
+      <c r="J60" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="str">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
         <v>테스트고객060</v>
       </c>
-      <c r="B61" t="str">
+      <c r="C61" t="str">
         <v>010-5500-1060</v>
       </c>
-      <c r="C61" t="str">
+      <c r="D61" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D61" t="str">
-        <v>경기도 광주시 벌원길 42, 151동 120호</v>
-      </c>
       <c r="E61" t="str">
+        <v>경기도 광주시 벌원길 42</v>
+      </c>
+      <c r="F61" t="str">
+        <v>151동 120호</v>
+      </c>
+      <c r="G61" t="str">
         <v>생활용품</v>
       </c>
-      <c r="F61" t="str">
+      <c r="H61" t="str">
         <v>T0060</v>
       </c>
-      <c r="G61">
+      <c r="I61">
         <v>4</v>
       </c>
-      <c r="H61" t="str">
+      <c r="J61" t="str">
         <v>부재 시 문고리에 걸어주세요</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="str">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
         <v>테스트고객061</v>
       </c>
-      <c r="B62" t="str">
+      <c r="C62" t="str">
         <v>010-5500-1061</v>
       </c>
-      <c r="C62" t="str">
+      <c r="D62" t="str">
         <v>경안동</v>
       </c>
-      <c r="D62" t="str">
-        <v>경기도 광주시 경안로 123-14, 161동 101호</v>
-      </c>
       <c r="E62" t="str">
+        <v>경기도 광주시 경안로 123-14</v>
+      </c>
+      <c r="F62" t="str">
+        <v>161동 101호</v>
+      </c>
+      <c r="G62" t="str">
         <v>채소</v>
       </c>
-      <c r="F62" t="str">
+      <c r="H62" t="str">
         <v>T0061</v>
       </c>
-      <c r="G62">
+      <c r="I62">
         <v>1</v>
       </c>
-      <c r="H62" t="str">
+      <c r="J62" t="str">
         <v>문 앞에 놓아주세요</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="str">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
         <v>테스트고객062</v>
       </c>
-      <c r="B63" t="str">
+      <c r="C63" t="str">
         <v>010-5500-1062</v>
       </c>
-      <c r="C63" t="str">
+      <c r="D63" t="str">
         <v>송정동</v>
       </c>
-      <c r="D63" t="str">
-        <v>경기도 광주시 경안천로 130, 171동 102호</v>
-      </c>
       <c r="E63" t="str">
+        <v>경기도 광주시 경안천로 130</v>
+      </c>
+      <c r="F63" t="str">
+        <v>171동 102호</v>
+      </c>
+      <c r="G63" t="str">
         <v>과일</v>
       </c>
-      <c r="F63" t="str">
+      <c r="H63" t="str">
         <v>T0062</v>
       </c>
-      <c r="G63">
+      <c r="I63">
         <v>2</v>
       </c>
-      <c r="H63" t="str">
+      <c r="J63" t="str">
         <v>도착 전 전화 부탁드립니다</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="str">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
         <v>테스트고객063</v>
       </c>
-      <c r="B64" t="str">
+      <c r="C64" t="str">
         <v>010-5500-1063</v>
       </c>
-      <c r="C64" t="str">
+      <c r="D64" t="str">
         <v>쌍령동</v>
       </c>
-      <c r="D64" t="str">
-        <v>경기도 광주시 경충대로 1439, 181동 103호</v>
-      </c>
       <c r="E64" t="str">
+        <v>경기도 광주시 경충대로 1439</v>
+      </c>
+      <c r="F64" t="str">
+        <v>181동 103호</v>
+      </c>
+      <c r="G64" t="str">
         <v>정육</v>
       </c>
-      <c r="F64" t="str">
+      <c r="H64" t="str">
         <v>T0063</v>
       </c>
-      <c r="G64">
+      <c r="I64">
         <v>3</v>
       </c>
-      <c r="H64" t="str">
+      <c r="J64" t="str">
         <v>천천히 오셔도 됩니다</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="str">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
         <v>테스트고객064</v>
       </c>
-      <c r="B65" t="str">
+      <c r="C65" t="str">
         <v>010-5500-1064</v>
       </c>
-      <c r="C65" t="str">
+      <c r="D65" t="str">
         <v>탄벌동</v>
       </c>
-      <c r="D65" t="str">
-        <v>경기도 광주시 벌원길 43, 101동 104호</v>
-      </c>
       <c r="E65" t="str">
+        <v>경기도 광주시 벌원길 43</v>
+      </c>
+      <c r="F65" t="str">
+        <v>101동 104호</v>
+      </c>
+      <c r="G65" t="str">
         <v>생선</v>
       </c>
-      <c r="F65" t="str">
+      <c r="H65" t="str">
         <v>T0064</v>
       </c>
-      <c r="G65">
+      <c r="I65">
         <v>4</v>
       </c>
-      <c r="H65" t="str">
+      <c r="J65" t="str">
         <v>벨 누르지 말아주세요</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="str">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
         <v>테스트고객065</v>
       </c>
-      <c r="B66" t="str">
+      <c r="C66" t="str">
         <v>010-5500-1065</v>
       </c>
-      <c r="C66" t="str">
+      <c r="D66" t="str">
         <v>경안동</v>
       </c>
-      <c r="D66" t="str">
-        <v>경기도 광주시 경안로 123-9, 111동 105호</v>
-      </c>
       <c r="E66" t="str">
+        <v>경기도 광주시 경안로 123-9</v>
+      </c>
+      <c r="F66" t="str">
+        <v>111동 105호</v>
+      </c>
+      <c r="G66" t="str">
         <v>반찬</v>
       </c>
-      <c r="F66" t="str">
+      <c r="H66" t="str">
         <v>T0065</v>
       </c>
-      <c r="G66">
+      <c r="I66">
         <v>1</v>
       </c>
-      <c r="H66" t="str">
+      <c r="J66" t="str">
         <v>경비실 호출 후 전달</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H66"/>
+  <autoFilter ref="A1:J66"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J66"/>
   </ignoredErrors>
 </worksheet>
 </file>